--- a/astro-site/public/dl/guia-chocolateria-obrador/checklist-equipamiento-y-proveedores-cacao.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/checklist-equipamiento-y-proveedores-cacao.xlsx
@@ -404,12 +404,12 @@
   <commentList>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Enumerados los 55 grupos del Anexo: 435, 439, 442, 452, 454, 474, 491, 495, 615, 641-647, 651-659, 662, 665, 691, 75... · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
+        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Enumerados los 55 grupos del Anexo: 435, 439, 442, 452, 454, 474, 491, 495, 615, 641-647, 651-659, 662, 665,...) · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
       </text>
     </comment>
     <comment ref="C30" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) (El art. 3 exige tres condiciones acumulativas: libres de deforestación, producidos conforme a la legislación del país de produc... · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
+        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) (Arts.) · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
       </text>
     </comment>
     <comment ref="C34" authorId="0" shapeId="0">
@@ -439,7 +439,7 @@
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
+        <t>Verificado el 12-09-2026 · Reglamento (UE) 2023/1115 del Parlamento Europeo y del Consejo, de 31 de mayo de 2023 (EUDR) · texto consolidado CELEX:02023R1115-20251226 (versión 26-12-2025, 002.001) (Arts.) · https://eur-lex.europa.eu/legal-content/ES/TXT/HTML/?uri=CELEX:02023R1115-20251226</t>
       </text>
     </comment>
     <comment ref="K6" authorId="0" shapeId="0">
@@ -479,7 +479,7 @@
     </comment>
     <comment ref="A38" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Real Decreto 1021/2022 (BOE-A-2022-21681), arts. 2.2.a), 3.1 y 4.3 (16 (CHN-90) y por la lectura directa del art. 4.3 (CHN-88).) · https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681</t>
+        <t>Verificado el 12-09-2026 · Real Decreto 1021/2022 (BOE-A-2022-21681), arts. 2.2.a), 3.1 y 4.3 · https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681</t>
       </text>
     </comment>
   </commentList>
